--- a/admin/wallets.xlsx
+++ b/admin/wallets.xlsx
@@ -478,7 +478,7 @@
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>Seed Phrase</t>
+          <t>Encrypted Seed</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
@@ -519,11 +519,6 @@
           <t>IMPORTED</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>ocean swift rain golden fire river moon star forest calm mountain tree</t>
-        </is>
-      </c>
       <c r="I2" t="inlineStr">
         <is>
           <t>assets\d383f0b5_f8b2d8524081faefa39d9e657267fc29.jpg</t>
@@ -562,11 +557,6 @@
           <t>CREATED</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>ocean swift rain golden fire river moon star forest calm mountain tree</t>
-        </is>
-      </c>
       <c r="I3" t="inlineStr">
         <is>
           <t>None</t>
@@ -605,11 +595,6 @@
           <t>CREATED</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>silver golden cloud sky mountain star tree rain swift cloud fire stone</t>
-        </is>
-      </c>
       <c r="I4" t="inlineStr">
         <is>
           <t>assets\337b6f35_8e21c9809218091e7a2bf7f3514b4c3b.jpg</t>
@@ -648,11 +633,6 @@
           <t>CREATED</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>forest cloud silver thunder cloud apple sky fire ocean moon swift mountain</t>
-        </is>
-      </c>
       <c r="I5" t="inlineStr">
         <is>
           <t>assets\f1493e56_6d32feb4bb0cf4ceb3d7fb336e4904b8.jpg</t>
@@ -691,11 +671,6 @@
           <t>CREATED</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>river tree star mountain cloud wind silver sun cloud sky bright forest</t>
-        </is>
-      </c>
       <c r="I6" t="inlineStr">
         <is>
           <t>assets\8732f94f_6d32feb4bb0cf4ceb3d7fb336e4904b8.jpg</t>
@@ -734,11 +709,6 @@
           <t>CREATED</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>ocean calm silver cloud swift moon cloud fire forest thunder sun star</t>
-        </is>
-      </c>
       <c r="I7" t="inlineStr">
         <is>
           <t>assets\50da15b2_6d32feb4bb0cf4ceb3d7fb336e4904b8.jpg</t>
@@ -775,11 +745,6 @@
       <c r="G8" t="inlineStr">
         <is>
           <t>CREATED</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>cloud silver beach fire moon sun calm bright forest thunder swift sky</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
